--- a/Sindhi Muslim/Salary Sheet/Salary Sheet - January-2024.xlsx
+++ b/Sindhi Muslim/Salary Sheet/Salary Sheet - January-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Salary Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D84E96-6408-45F3-9D5E-D8ECAFD870BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999C2EFC-9937-4F35-AD98-C06326BFC88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{92CE3A9B-E618-454F-A242-AE026DF5BDF3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="83">
   <si>
     <t xml:space="preserve">Government High School Sindhi Jamaat Cooperative Housing Society, Bin Qasim Town Karachi </t>
   </si>
@@ -243,9 +243,6 @@
     <t>31201 2460819 2</t>
   </si>
   <si>
-    <t>Salary Sheet for the Month November 2024</t>
-  </si>
-  <si>
     <t>Nusrat</t>
   </si>
   <si>
@@ -283,6 +280,12 @@
   </si>
   <si>
     <t>31201-6578084-1</t>
+  </si>
+  <si>
+    <t>Signature</t>
+  </si>
+  <si>
+    <t>Salary Sheet for the Month January 2025</t>
   </si>
 </sst>
 </file>
@@ -409,7 +412,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -511,35 +514,69 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -551,144 +588,19 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -696,50 +608,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -758,165 +653,124 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -985,17 +839,9 @@
           <cell r="AJ20">
             <v>0</v>
           </cell>
-          <cell r="AK20">
-            <v>0</v>
-          </cell>
         </row>
         <row r="21">
           <cell r="AJ21">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="AK22">
             <v>0</v>
           </cell>
         </row>
@@ -1003,23 +849,14 @@
           <cell r="AJ23">
             <v>0</v>
           </cell>
-          <cell r="AK23">
-            <v>0</v>
-          </cell>
         </row>
         <row r="24">
           <cell r="AJ24">
             <v>0</v>
           </cell>
-          <cell r="AK24">
-            <v>0</v>
-          </cell>
         </row>
         <row r="25">
           <cell r="AJ25">
-            <v>0</v>
-          </cell>
-          <cell r="AK25">
             <v>0</v>
           </cell>
         </row>
@@ -1344,63 +1181,65 @@
     <col min="12" max="12" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.140625" customWidth="1"/>
     <col min="14" max="14" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
-      <c r="J1" s="70"/>
-      <c r="K1" s="70"/>
-      <c r="L1" s="70"/>
-      <c r="M1" s="70"/>
-      <c r="N1" s="71"/>
-    </row>
-    <row r="2" spans="1:15" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="74"/>
-    </row>
-    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="47" t="s">
+      <c r="A1" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+    </row>
+    <row r="2" spans="1:15" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+    </row>
+    <row r="4" spans="1:15" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A4" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="49"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -1419,427 +1258,431 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="56" t="s">
+      <c r="G6" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="56" t="s">
+      <c r="H6" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="75" t="s">
+      <c r="I6" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="76" t="s">
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="66" t="s">
+      <c r="N6" s="42" t="s">
         <v>12</v>
       </c>
+      <c r="O6" s="49" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="43" t="s">
+      <c r="A7" s="23"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="43" t="s">
+      <c r="J7" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="43" t="s">
+      <c r="K7" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="45" t="s">
+      <c r="L7" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="77"/>
-      <c r="N7" s="67"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="50"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="52"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="78"/>
-      <c r="N8" s="68"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A8" s="24"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="51"/>
+    </row>
+    <row r="9" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="18">
         <v>44774</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="38" t="s">
+      <c r="G9" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="19">
         <v>24200</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="9">
+        <v>31</v>
+      </c>
+      <c r="J9" s="9">
         <v>30</v>
       </c>
-      <c r="J9" s="15">
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9"/>
+      <c r="N9" s="46">
+        <v>24200</v>
+      </c>
+      <c r="O9" s="47"/>
+    </row>
+    <row r="10" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="5">
+        <v>44774</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="8">
+        <v>16500</v>
+      </c>
+      <c r="I10" s="4">
+        <v>31</v>
+      </c>
+      <c r="J10" s="4">
         <v>30</v>
       </c>
-      <c r="K9" s="15">
-        <v>0</v>
-      </c>
-      <c r="L9" s="15">
-        <f>[1]Attandance!AK5</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="15"/>
-      <c r="N9" s="16">
-        <v>24200</v>
-      </c>
-      <c r="O9" s="34"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="N10" s="41">
+        <v>16500</v>
+      </c>
+      <c r="O10" s="43"/>
+    </row>
+    <row r="11" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="11">
-        <v>44774</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="14">
+      <c r="E11" s="5">
+        <v>45198</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="8">
         <v>16500</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I11" s="4">
+        <v>31</v>
+      </c>
+      <c r="J11" s="4">
         <v>30</v>
       </c>
-      <c r="J10" s="15">
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <v>1</v>
+      </c>
+      <c r="M11" s="4"/>
+      <c r="N11" s="41">
+        <v>16500</v>
+      </c>
+      <c r="O11" s="43"/>
+    </row>
+    <row r="12" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="5">
+        <v>45323</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="8">
+        <v>25000</v>
+      </c>
+      <c r="I12" s="4">
+        <v>31</v>
+      </c>
+      <c r="J12" s="4">
         <v>30</v>
       </c>
-      <c r="K10" s="10">
-        <v>0</v>
-      </c>
-      <c r="L10" s="10">
-        <v>0</v>
-      </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="35">
-        <v>16500</v>
-      </c>
-      <c r="O10" s="34"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4">
+        <v>1</v>
+      </c>
+      <c r="M12" s="4"/>
+      <c r="N12" s="41">
+        <v>25000</v>
+      </c>
+      <c r="O12" s="43"/>
+    </row>
+    <row r="13" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="11">
-        <v>45198</v>
-      </c>
-      <c r="F11" s="12" t="s">
+      <c r="E13" s="5">
+        <v>45536</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="8">
+        <v>20000</v>
+      </c>
+      <c r="I13" s="4">
+        <v>31</v>
+      </c>
+      <c r="J13" s="4">
+        <v>30</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4"/>
+      <c r="N13" s="41">
+        <v>20000</v>
+      </c>
+      <c r="O13" s="43"/>
+    </row>
+    <row r="14" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="5">
+        <v>45566</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="8">
+        <v>30000</v>
+      </c>
+      <c r="I14" s="4">
+        <v>31</v>
+      </c>
+      <c r="J14" s="4">
+        <v>30</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4">
+        <v>1</v>
+      </c>
+      <c r="M14" s="4"/>
+      <c r="N14" s="41">
+        <v>30000</v>
+      </c>
+      <c r="O14" s="43"/>
+    </row>
+    <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="5">
+        <v>45597</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="8">
+        <v>30000</v>
+      </c>
+      <c r="I15" s="4">
+        <v>31</v>
+      </c>
+      <c r="J15" s="4">
+        <v>30</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4">
+        <v>1</v>
+      </c>
+      <c r="M15" s="4"/>
+      <c r="N15" s="41">
+        <v>30000</v>
+      </c>
+      <c r="O15" s="43"/>
+    </row>
+    <row r="16" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="12">
+        <v>45559</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="15">
+        <v>28000</v>
+      </c>
+      <c r="I16" s="11">
+        <v>31</v>
+      </c>
+      <c r="J16" s="11">
         <v>29</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="14">
-        <v>16500</v>
-      </c>
-      <c r="I11" s="10">
-        <v>30</v>
-      </c>
-      <c r="J11" s="15">
-        <v>30</v>
-      </c>
-      <c r="K11" s="10">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10">
-        <v>1</v>
-      </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="35">
-        <v>16500</v>
-      </c>
-      <c r="O11" s="34"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="11">
-        <v>45323</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="14">
-        <v>25000</v>
-      </c>
-      <c r="I12" s="10">
-        <v>30</v>
-      </c>
-      <c r="J12" s="15">
-        <v>30</v>
-      </c>
-      <c r="K12" s="10">
-        <v>0</v>
-      </c>
-      <c r="L12" s="10">
-        <v>1</v>
-      </c>
-      <c r="M12" s="10"/>
-      <c r="N12" s="35">
-        <v>25000</v>
-      </c>
-      <c r="O12" s="34"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="11">
-        <v>45536</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="14">
-        <v>20000</v>
-      </c>
-      <c r="I13" s="10">
-        <v>30</v>
-      </c>
-      <c r="J13" s="15">
-        <v>30</v>
-      </c>
-      <c r="K13" s="10">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10"/>
-      <c r="N13" s="35">
-        <v>20000</v>
-      </c>
-      <c r="O13" s="34"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="11">
-        <v>45566</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="14">
-        <v>30000</v>
-      </c>
-      <c r="I14" s="10">
-        <v>30</v>
-      </c>
-      <c r="J14" s="15">
-        <v>30</v>
-      </c>
-      <c r="K14" s="10">
-        <v>0</v>
-      </c>
-      <c r="L14" s="10">
-        <v>1</v>
-      </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="35">
-        <v>30000</v>
-      </c>
-      <c r="O14" s="34"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="11">
-        <v>45597</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="H15" s="14">
-        <v>30000</v>
-      </c>
-      <c r="I15" s="10">
-        <v>30</v>
-      </c>
-      <c r="J15" s="10">
-        <v>30</v>
-      </c>
-      <c r="K15" s="10">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10">
-        <v>1</v>
-      </c>
-      <c r="M15" s="10"/>
-      <c r="N15" s="35">
-        <v>30000</v>
-      </c>
-      <c r="O15" s="34"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="19">
-        <v>45559</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="22">
-        <v>28000</v>
-      </c>
-      <c r="I16" s="18">
-        <v>30</v>
-      </c>
-      <c r="J16" s="18">
-        <v>28</v>
-      </c>
-      <c r="K16" s="18">
+      <c r="K16" s="11">
         <v>2</v>
       </c>
-      <c r="L16" s="18">
-        <v>0</v>
-      </c>
-      <c r="M16" s="24"/>
-      <c r="N16" s="36">
+      <c r="L16" s="11">
+        <v>0</v>
+      </c>
+      <c r="M16" s="16"/>
+      <c r="N16" s="44">
         <v>26133.33</v>
       </c>
-      <c r="O16" s="34"/>
+      <c r="O16" s="45"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
@@ -1857,7 +1700,7 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1873,23 +1716,24 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:15" ht="27" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="47" t="s">
+    <row r="19" spans="1:15" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A19" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="49"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="53"/>
     </row>
     <row r="20" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -1908,399 +1752,425 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="53" t="s">
+      <c r="D21" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="E21" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="59" t="s">
+      <c r="G21" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="H21" s="59" t="s">
+      <c r="H21" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="I21" s="62" t="s">
+      <c r="I21" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="62"/>
-      <c r="M21" s="63" t="s">
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="N21" s="66" t="s">
+      <c r="N21" s="42" t="s">
         <v>12</v>
       </c>
+      <c r="O21" s="49" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="51"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="39" t="s">
+      <c r="A22" s="23"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="J22" s="39" t="s">
+      <c r="J22" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="K22" s="39" t="s">
+      <c r="K22" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="L22" s="41" t="s">
+      <c r="L22" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="M22" s="64"/>
-      <c r="N22" s="67"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="50"/>
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="52"/>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="68"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A23" s="24"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="37"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="51"/>
+    </row>
+    <row r="24" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="18">
         <v>44475</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G24" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="H24" s="7">
+      <c r="G24" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="19">
         <v>66000</v>
       </c>
-      <c r="I24" s="4">
+      <c r="I24" s="9">
         <v>30</v>
       </c>
-      <c r="J24" s="4">
-        <v>0</v>
-      </c>
-      <c r="K24" s="4">
-        <v>0</v>
-      </c>
-      <c r="L24" s="4">
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
         <v>1</v>
       </c>
-      <c r="M24" s="26">
+      <c r="M24" s="60">
         <v>25000</v>
       </c>
-      <c r="N24" s="8">
+      <c r="N24" s="46">
         <v>91000</v>
       </c>
-      <c r="O24" s="79"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
+      <c r="O24" s="61"/>
+    </row>
+    <row r="25" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="5">
         <v>45468</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G25" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="29">
+      <c r="G25" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" s="8">
         <v>24000</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="4">
         <v>30</v>
       </c>
-      <c r="J25" s="15">
-        <v>0</v>
-      </c>
-      <c r="K25" s="15">
+      <c r="J25" s="4">
+        <v>0</v>
+      </c>
+      <c r="K25" s="4">
         <f>[1]Attandance!AJ20</f>
         <v>0</v>
       </c>
-      <c r="L25" s="15">
-        <f>[1]Attandance!AK20</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="16">
+      <c r="L25" s="4">
+        <v>0</v>
+      </c>
+      <c r="M25" s="4"/>
+      <c r="N25" s="41">
         <v>24000</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
+      <c r="O25" s="58"/>
+    </row>
+    <row r="26" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="5">
         <v>45505</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G26" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="29">
+      <c r="G26" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="8">
         <v>8000</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="4">
         <v>30</v>
       </c>
-      <c r="J26" s="15">
-        <v>0</v>
-      </c>
-      <c r="K26" s="15">
+      <c r="J26" s="4">
+        <v>0</v>
+      </c>
+      <c r="K26" s="4">
         <f>[1]Attandance!AJ21</f>
         <v>0</v>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="4">
         <v>1</v>
       </c>
-      <c r="M26" s="15"/>
-      <c r="N26" s="16">
+      <c r="M26" s="4"/>
+      <c r="N26" s="41">
         <v>8000</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="27" t="s">
+      <c r="O26" s="58"/>
+    </row>
+    <row r="27" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="C27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="5">
+        <v>45597</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="G27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H27" s="8">
+        <v>15000</v>
+      </c>
+      <c r="I27" s="4">
+        <v>30</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4"/>
+      <c r="N27" s="41">
+        <v>15000</v>
+      </c>
+      <c r="O27" s="58"/>
+    </row>
+    <row r="28" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="5">
+        <v>44967</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H28" s="8">
+        <v>16500</v>
+      </c>
+      <c r="I28" s="4">
+        <v>30</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4">
+        <f>[1]Attandance!AJ23</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="4">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4"/>
+      <c r="N28" s="41">
+        <v>16500</v>
+      </c>
+      <c r="O28" s="58"/>
+    </row>
+    <row r="29" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="5">
+        <v>45587</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H29" s="8">
+        <v>15000</v>
+      </c>
+      <c r="I29" s="4">
+        <v>30</v>
+      </c>
+      <c r="J29" s="4">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4">
+        <f>[1]Attandance!AJ24</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="4">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4"/>
+      <c r="N29" s="41">
+        <v>15000</v>
+      </c>
+      <c r="O29" s="58"/>
+    </row>
+    <row r="30" spans="1:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D30" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="28">
-        <v>45597</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="13" t="s">
+      <c r="E30" s="12">
+        <v>44959</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H27" s="29">
-        <v>15000</v>
-      </c>
-      <c r="I27" s="15">
+      <c r="H30" s="15">
+        <v>16500</v>
+      </c>
+      <c r="I30" s="11">
         <v>30</v>
       </c>
-      <c r="J27" s="15">
-        <v>0</v>
-      </c>
-      <c r="K27" s="15">
-        <v>0</v>
-      </c>
-      <c r="L27" s="15">
-        <f>[1]Attandance!AK22</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="16">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="28">
-        <v>44967</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H28" s="29">
+      <c r="J30" s="11">
+        <v>0</v>
+      </c>
+      <c r="K30" s="11">
+        <f>[1]Attandance!AJ25</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="11">
+        <v>0</v>
+      </c>
+      <c r="M30" s="11"/>
+      <c r="N30" s="44">
         <v>16500</v>
       </c>
-      <c r="I28" s="15">
-        <v>30</v>
-      </c>
-      <c r="J28" s="15">
-        <v>0</v>
-      </c>
-      <c r="K28" s="15">
-        <f>[1]Attandance!AJ23</f>
-        <v>0</v>
-      </c>
-      <c r="L28" s="15">
-        <f>[1]Attandance!AK23</f>
-        <v>0</v>
-      </c>
-      <c r="M28" s="15"/>
-      <c r="N28" s="16">
-        <v>16500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="28">
-        <v>45587</v>
-      </c>
-      <c r="F29" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="G29" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="H29" s="29">
-        <v>15000</v>
-      </c>
-      <c r="I29" s="15">
-        <v>30</v>
-      </c>
-      <c r="J29" s="15">
-        <v>0</v>
-      </c>
-      <c r="K29" s="15">
-        <f>[1]Attandance!AJ24</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="15">
-        <f>[1]Attandance!AK24</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="10"/>
-      <c r="N29" s="16">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="19">
-        <v>44959</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" s="33">
-        <v>16500</v>
-      </c>
-      <c r="I30" s="23">
-        <v>30</v>
-      </c>
-      <c r="J30" s="23">
-        <v>0</v>
-      </c>
-      <c r="K30" s="23">
-        <f>[1]Attandance!AJ25</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="23">
-        <f>[1]Attandance!AK25</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="23"/>
-      <c r="N30" s="25">
-        <v>16500</v>
-      </c>
+      <c r="O30" s="59"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="36">
+    <mergeCell ref="O21:O23"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="M21:M23"/>
+    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="L22:L23"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="I21:L21"/>
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="J22:J23"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A4:N4"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
@@ -2310,42 +2180,24 @@
     <mergeCell ref="G6:G8"/>
     <mergeCell ref="H6:H8"/>
     <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="L22:L23"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A19:N19"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="M21:M23"/>
-    <mergeCell ref="N21:N23"/>
   </mergeCells>
-  <conditionalFormatting sqref="B9:M9 B10:C11 F24:F30 G25:I29 D25:E30 K25:M30 G30:J30 M10:M15 C12:C15 D10:L16">
-    <cfRule type="expression" dxfId="0" priority="4">
+  <conditionalFormatting sqref="B9:M9 B10:C11 M10:M15 D10:L16 C12:C15 F24:F30 G25:I29 D25:E30 K25:M30 G30:J30">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$C9=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C30">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$C24=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:E24 H24:M24 B24:B29 J25:J29">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$C24=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G24">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C24=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
